--- a/Decks/Tayam.xlsx
+++ b/Decks/Tayam.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\Magic\Decks\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD44E7FA-2FC3-477F-BA98-66C2F15236BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7DDAB5-3DCF-4C3F-B384-5FE29522D19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{944147F2-0001-441C-AD21-D02E4373DFF7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="108">
   <si>
     <t>Função</t>
   </si>
@@ -170,9 +170,6 @@
     <t>Maester Seymour</t>
   </si>
   <si>
-    <t>Sphere Grid</t>
-  </si>
-  <si>
     <t>Tromell, Seymour's Butler</t>
   </si>
   <si>
@@ -239,9 +236,6 @@
     <t>Abzan Falconer</t>
   </si>
   <si>
-    <t>Tuskguard Captain</t>
-  </si>
-  <si>
     <t>Court of Garenbrig</t>
   </si>
   <si>
@@ -335,9 +329,6 @@
     <t>Michelangelo, Weirdness to 11</t>
   </si>
   <si>
-    <t>Omnivorous Flytrap</t>
-  </si>
-  <si>
     <t>Aron, Benalia's Ruin</t>
   </si>
   <si>
@@ -363,6 +354,12 @@
   </si>
   <si>
     <t>Wildgroth Archaic</t>
+  </si>
+  <si>
+    <t>Omnivorus Flytrap</t>
+  </si>
+  <si>
+    <t>Turkguard Captain</t>
   </si>
 </sst>
 </file>
@@ -1017,7 +1014,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
         <v>25</v>
@@ -1032,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1077,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1512,10 +1509,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D49" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1542,10 +1539,10 @@
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D51" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1557,13 +1554,10 @@
         <v>1</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="D52" t="s">
-        <v>44</v>
-      </c>
-      <c r="E52" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1575,10 +1569,10 @@
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D53" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1590,10 +1584,10 @@
         <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="D54" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1605,10 +1599,10 @@
         <v>0</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D55" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -1620,10 +1614,10 @@
         <v>1</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>49</v>
+        <v>86</v>
       </c>
       <c r="D56" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -1635,10 +1629,10 @@
         <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D57" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -1650,10 +1644,10 @@
         <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D58" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="F58"/>
     </row>
@@ -1666,10 +1660,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D59" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -1681,10 +1675,10 @@
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D60" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -1696,10 +1690,10 @@
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D61" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -1711,10 +1705,10 @@
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D62" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -1726,10 +1720,10 @@
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D63" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -1741,10 +1735,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D64" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -1752,14 +1746,14 @@
         <v>42</v>
       </c>
       <c r="B65" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
+        <f>C65&lt;&gt;D65</f>
+        <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="D65" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -1771,10 +1765,10 @@
         <v>1</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D66" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -1782,530 +1776,530 @@
         <v>42</v>
       </c>
       <c r="B67" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C67&lt;&gt;D67</f>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
       <c r="D67" t="s">
-        <v>58</v>
+        <v>97</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="B68" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C68&lt;&gt;D68</f>
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D68" t="s">
-        <v>100</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="F68" s="4"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>59</v>
+        <v>42</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D69" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D70" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>58</v>
+      </c>
+      <c r="B71" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B71" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>62</v>
-      </c>
       <c r="D71" t="s">
-        <v>62</v>
-      </c>
-      <c r="F71"/>
+        <v>59</v>
+      </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D72" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="D73" t="s">
-        <v>64</v>
-      </c>
+        <v>61</v>
+      </c>
+      <c r="F73"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D74" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D75" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D76" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="D77" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B78" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C78&lt;&gt;D78</f>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D78" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="D79" t="s">
-        <v>71</v>
-      </c>
-      <c r="F79" s="4"/>
+        <v>68</v>
+      </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>67</v>
+      </c>
+      <c r="B80" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D80" t="s">
         <v>69</v>
       </c>
-      <c r="B80" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="D80" t="s">
-        <v>72</v>
-      </c>
-      <c r="E80" s="4"/>
       <c r="F80" s="4"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D81" t="s">
-        <v>73</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="E81" s="4"/>
       <c r="F81" s="4"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B82" s="5" t="b">
-        <f>C82&lt;&gt;D82</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>41</v>
+        <v>71</v>
       </c>
       <c r="D82" t="s">
-        <v>41</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F82" s="4"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B83" s="5" t="b">
         <f>C83&lt;&gt;D83</f>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="D83" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B84" s="5" t="b">
         <f>C84&lt;&gt;D84</f>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D84" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B85" s="5" t="b">
-        <f t="shared" si="1"/>
+        <f>C85&lt;&gt;D85</f>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="D85" t="s">
-        <v>95</v>
-      </c>
-      <c r="F85" s="4"/>
+        <v>87</v>
+      </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D86" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D87" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D88" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="D89" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>72</v>
+      </c>
+      <c r="B90" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B90" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>76</v>
-      </c>
       <c r="D90" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B91" s="5" t="b">
         <f>C91&lt;&gt;D91</f>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D91" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D92" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D93" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>76</v>
+      </c>
+      <c r="B94" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B94" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>80</v>
-      </c>
       <c r="D94" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D95" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D96" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D97" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D98" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D99" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D100" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="D101" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Tayam.xlsx
+++ b/Decks/Tayam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F7DDAB5-3DCF-4C3F-B384-5FE29522D19D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FC42DC-C9BC-4F6E-9964-A88768274D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{944147F2-0001-441C-AD21-D02E4373DFF7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="109">
   <si>
     <t>Função</t>
   </si>
@@ -360,6 +360,9 @@
   </si>
   <si>
     <t>Turkguard Captain</t>
+  </si>
+  <si>
+    <t>Nesting Grounds</t>
   </si>
 </sst>
 </file>
@@ -1089,10 +1092,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>9</v>
+        <v>108</v>
       </c>
       <c r="D22" t="s">
-        <v>9</v>
+        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">

--- a/Decks/Tayam.xlsx
+++ b/Decks/Tayam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FC42DC-C9BC-4F6E-9964-A88768274D8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F3BACF-F242-4E47-9127-6CA1E9EF4CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{944147F2-0001-441C-AD21-D02E4373DFF7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="108">
   <si>
     <t>Função</t>
   </si>
@@ -155,9 +155,6 @@
     <t>Sakura-Tribe Elder</t>
   </si>
   <si>
-    <t>Jiang Yanguu, Wildcrafter</t>
-  </si>
-  <si>
     <t>Wood Elves</t>
   </si>
   <si>
@@ -203,9 +200,6 @@
     <t>Shelinda, Yevon Acolyte</t>
   </si>
   <si>
-    <t>Ardbert, Warrior of Darkness</t>
-  </si>
-  <si>
     <t>Master Chef</t>
   </si>
   <si>
@@ -353,16 +347,19 @@
     <t>Duty Beyond Death</t>
   </si>
   <si>
-    <t>Wildgroth Archaic</t>
-  </si>
-  <si>
-    <t>Omnivorus Flytrap</t>
-  </si>
-  <si>
-    <t>Turkguard Captain</t>
-  </si>
-  <si>
     <t>Nesting Grounds</t>
+  </si>
+  <si>
+    <t>Jiang Yanggu, Wildcrafter</t>
+  </si>
+  <si>
+    <t>Wildgrowth Archaic</t>
+  </si>
+  <si>
+    <t>Omnivorous Flytrap</t>
+  </si>
+  <si>
+    <t>Tuskguard Captain</t>
   </si>
 </sst>
 </file>
@@ -1032,10 +1029,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D18" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1077,10 +1074,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1092,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1482,10 +1479,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="D47" t="s">
-        <v>39</v>
+        <v>104</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1497,10 +1494,10 @@
         <v>0</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D48" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1512,75 +1509,75 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="5" t="b">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B50" s="5" t="b">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>43</v>
-      </c>
       <c r="D50" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B51" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D51" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B52" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D52" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B53" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D53" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B54" s="5" t="b">
         <f t="shared" si="0"/>
@@ -1595,340 +1592,340 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B55" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D55" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B56" s="5" t="b">
         <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="D56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B57" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D57" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B58" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D58" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="F58"/>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B59" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D59" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B60" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D60" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B61" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D61" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B62" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D62" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B63" s="5" t="b">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D63" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B64" s="5" t="b">
         <f t="shared" ref="B64:B101" si="1">C64&lt;&gt;D64</f>
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D64" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B65" s="5" t="b">
         <f>C65&lt;&gt;D65</f>
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D65" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B66" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="D66" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B67" s="5" t="b">
         <f>C67&lt;&gt;D67</f>
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="D67" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B68" s="5" t="b">
         <f>C68&lt;&gt;D68</f>
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D68" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F68" s="4"/>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B69" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D69" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D70" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B71" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D71" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>56</v>
+      </c>
+      <c r="B72" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C72" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B72" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="D72" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D73" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F73"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D74" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D75" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D76" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
@@ -1938,181 +1935,181 @@
         <v>106</v>
       </c>
       <c r="D77" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B78" s="5" t="b">
         <f>C78&lt;&gt;D78</f>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D78" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B79" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D79" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
+        <v>65</v>
+      </c>
+      <c r="B80" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D80" t="s">
         <v>67</v>
-      </c>
-      <c r="B80" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="D80" t="s">
-        <v>69</v>
       </c>
       <c r="F80" s="4"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D81" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D82" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="F82" s="4"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B83" s="5" t="b">
         <f>C83&lt;&gt;D83</f>
         <v>0</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D83" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B84" s="5" t="b">
         <f>C84&lt;&gt;D84</f>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D84" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B85" s="5" t="b">
         <f>C85&lt;&gt;D85</f>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D85" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B86" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D86" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="D87" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D88" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
@@ -2122,187 +2119,187 @@
         <v>107</v>
       </c>
       <c r="D89" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>70</v>
+      </c>
+      <c r="B90" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C90" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B90" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>74</v>
-      </c>
       <c r="D90" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B91" s="5" t="b">
         <f>C91&lt;&gt;D91</f>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D91" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D92" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B93" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D93" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
+        <v>74</v>
+      </c>
+      <c r="B94" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C94" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B94" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>78</v>
-      </c>
       <c r="D94" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D95" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D96" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D97" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D98" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D99" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D100" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D101" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/Decks/Tayam.xlsx
+++ b/Decks/Tayam.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Marcelo Scalvi\Dropbox\Jogos\TheMagicCollection\Decks\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F3BACF-F242-4E47-9127-6CA1E9EF4CA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C2801B8-C083-4F4F-BF0F-4834286F22C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{944147F2-0001-441C-AD21-D02E4373DFF7}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="107">
   <si>
     <t>Função</t>
   </si>
@@ -177,9 +177,6 @@
   </si>
   <si>
     <t>Anafenza, Kin-Tree Spirit</t>
-  </si>
-  <si>
-    <t>Botanical Brawler</t>
   </si>
   <si>
     <t>Champion of Lambholt</t>
@@ -1029,10 +1026,10 @@
         <v>0</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D18" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1074,10 +1071,10 @@
         <v>0</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D21" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1089,10 +1086,10 @@
         <v>0</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D22" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1479,10 +1476,10 @@
         <v>0</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D47" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -1509,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D49" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1539,10 +1536,10 @@
         <v>0</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D51" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1554,10 +1551,10 @@
         <v>1</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D52" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1584,10 +1581,10 @@
         <v>0</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D54" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1614,7 +1611,7 @@
         <v>1</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D56" t="s">
         <v>45</v>
@@ -1644,10 +1641,10 @@
         <v>0</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D58" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F58"/>
     </row>
@@ -1660,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D59" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -1675,10 +1672,10 @@
         <v>0</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D60" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -1690,10 +1687,10 @@
         <v>0</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D61" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -1705,10 +1702,10 @@
         <v>0</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D62" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -1720,10 +1717,10 @@
         <v>0</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D63" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -1735,10 +1732,10 @@
         <v>0</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D64" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -1750,10 +1747,10 @@
         <v>0</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D65" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -1765,10 +1762,10 @@
         <v>0</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D66" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -1780,10 +1777,10 @@
         <v>0</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D67" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -1795,10 +1792,10 @@
         <v>0</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D68" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F68" s="4"/>
     </row>
@@ -1811,215 +1808,215 @@
         <v>1</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D69" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B70" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D70" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>55</v>
+      </c>
+      <c r="B71" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C71" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B71" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>57</v>
-      </c>
       <c r="D71" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B72" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D72" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B73" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D73" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="F73"/>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B74" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D74" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D75" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B76" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D76" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B77" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D77" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B78" s="5" t="b">
         <f>C78&lt;&gt;D78</f>
         <v>0</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D78" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>64</v>
+      </c>
+      <c r="B79" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C79" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="B79" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>66</v>
-      </c>
       <c r="D79" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B80" s="5" t="b">
         <f t="shared" si="1"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="D80" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F80" s="4"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B81" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D81" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E81" s="4"/>
       <c r="F81" s="4"/>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B82" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D82" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F82" s="4"/>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B83" s="5" t="b">
         <f>C83&lt;&gt;D83</f>
@@ -2034,272 +2031,272 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B84" s="5" t="b">
         <f>C84&lt;&gt;D84</f>
         <v>0</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D84" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B85" s="5" t="b">
         <f>C85&lt;&gt;D85</f>
         <v>0</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D85" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
+        <v>69</v>
+      </c>
+      <c r="B86" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B86" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>71</v>
-      </c>
       <c r="D86" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B87" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D87" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B88" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D88" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B89" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D89" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B90" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D90" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B91" s="5" t="b">
         <f>C91&lt;&gt;D91</f>
         <v>0</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D91" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B92" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D92" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
+        <v>73</v>
+      </c>
+      <c r="B93" s="5" t="b">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="C93" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B93" s="5" t="b">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>75</v>
-      </c>
       <c r="D93" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B94" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D94" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B95" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D95" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B96" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D96" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B97" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D97" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B98" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D98" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B99" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D99" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B100" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D100" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B101" s="5" t="b">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D101" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>
